--- a/docs/Results/States/pop_results_Sachsen_CT_vs_Stroke.xlsx
+++ b/docs/Results/States/pop_results_Sachsen_CT_vs_Stroke.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>1521923</v>
+        <v>708201</v>
       </c>
       <c r="D2" t="n">
-        <v>36.95</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>3197262</v>
+        <v>1939386</v>
       </c>
       <c r="D3" t="n">
-        <v>77.63</v>
+        <v>47.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>3889236</v>
+        <v>3113673</v>
       </c>
       <c r="D4" t="n">
-        <v>94.43000000000001</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Stroke Units</t>
+          <t>Hospitals with CT</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>4098549</v>
+        <v>3797134</v>
       </c>
       <c r="D5" t="n">
-        <v>99.52</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>3223523</v>
+        <v>4017391</v>
       </c>
       <c r="D6" t="n">
-        <v>78.27</v>
+        <v>97.54000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +540,10 @@
         <v>30</v>
       </c>
       <c r="C7" t="n">
-        <v>4104671</v>
+        <v>4020523</v>
       </c>
       <c r="D7" t="n">
-        <v>99.66</v>
+        <v>97.62</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>4117206</v>
+        <v>4107283</v>
       </c>
       <c r="D8" t="n">
-        <v>99.97</v>
+        <v>99.73</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,461 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4115622</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.93000000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4117589</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4117629</v>
+      </c>
+      <c r="D11" t="n">
+        <v>99.98</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>55</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4117174</v>
+      </c>
+      <c r="D12" t="n">
+        <v>99.97</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hospitals with CT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>60</v>
       </c>
-      <c r="C9" t="n">
-        <v>4117571</v>
-      </c>
-      <c r="D9" t="n">
-        <v>99.98</v>
+      <c r="C13" t="n">
+        <v>4117391</v>
+      </c>
+      <c r="D13" t="n">
+        <v>99.97</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>294506</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1021366</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1819784</v>
+      </c>
+      <c r="D16" t="n">
+        <v>44.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2576840</v>
+      </c>
+      <c r="D17" t="n">
+        <v>62.57</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3096419</v>
+      </c>
+      <c r="D18" t="n">
+        <v>75.18000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>30</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3427441</v>
+      </c>
+      <c r="D19" t="n">
+        <v>83.22</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3690031</v>
+      </c>
+      <c r="D20" t="n">
+        <v>89.59999999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>40</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3856803</v>
+      </c>
+      <c r="D21" t="n">
+        <v>93.65000000000001</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>45</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3961437</v>
+      </c>
+      <c r="D22" t="n">
+        <v>96.19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4050330</v>
+      </c>
+      <c r="D23" t="n">
+        <v>98.34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>55</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4095184</v>
+      </c>
+      <c r="D24" t="n">
+        <v>99.43000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Extended Stroke Hospitals</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>60</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4112355</v>
+      </c>
+      <c r="D25" t="n">
+        <v>99.84999999999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>247330</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>876436</v>
+      </c>
+      <c r="D27" t="n">
+        <v>21.28</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1522012</v>
+      </c>
+      <c r="D28" t="n">
+        <v>36.96</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>20</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2222827</v>
+      </c>
+      <c r="D29" t="n">
+        <v>53.97</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2812403</v>
+      </c>
+      <c r="D30" t="n">
+        <v>68.29000000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3197733</v>
+      </c>
+      <c r="D31" t="n">
+        <v>77.64</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>35</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3501038</v>
+      </c>
+      <c r="D32" t="n">
+        <v>85.01000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>40</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3739363</v>
+      </c>
+      <c r="D33" t="n">
+        <v>90.79000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>45</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3888125</v>
+      </c>
+      <c r="D34" t="n">
+        <v>94.41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>50</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4000047</v>
+      </c>
+      <c r="D35" t="n">
+        <v>97.12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>55</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4066955</v>
+      </c>
+      <c r="D36" t="n">
+        <v>98.75</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Stroke Units</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>60</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4098687</v>
+      </c>
+      <c r="D37" t="n">
+        <v>99.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Results/States/pop_results_Sachsen_CT_vs_Stroke.xlsx
+++ b/docs/Results/States/pop_results_Sachsen_CT_vs_Stroke.xlsx
@@ -645,7 +645,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -661,7 +661,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -677,7 +677,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -693,7 +693,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -709,7 +709,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -725,7 +725,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -741,7 +741,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -757,7 +757,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -773,7 +773,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -789,7 +789,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -805,7 +805,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -821,7 +821,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Extended Stroke Hospitals</t>
+          <t>Stroke-Ready Hospitals</t>
         </is>
       </c>
       <c r="B25" t="n">
